--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
   <si>
     <t>Filename</t>
   </si>
@@ -811,703 +811,682 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9870,0.0017,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.9962,0.0026,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.5745,0.0000,0.0000,0.7906</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9805,0.0002,0.0091,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.9877,0.0047,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.0075,0.0000,0.0002,0.9980</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0030,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0030,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.8714,0.0025,0.1046,0.0003</t>
+  </si>
+  <si>
+    <t>0.0045,0.0010,0.9944,0.0003</t>
+  </si>
+  <si>
+    <t>0.7537,0.0006,0.3668,0.0000</t>
+  </si>
+  <si>
+    <t>0.0083,0.0007,0.9906,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0001,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6390,0.3640,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8087,0.0002,0.2317,0.0002</t>
+  </si>
+  <si>
+    <t>0.9613,0.0001,0.0501,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0000,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.1207,0.8773,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9749,0.0061,0.0086,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0042</t>
+  </si>
+  <si>
+    <t>0.0037,0.8695,0.1250,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0071,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9907,0.0015,0.0061,0.0003</t>
+  </si>
+  <si>
+    <t>0.1273,0.9019,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.9952,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.0204,0.9113,0.0414,0.0057</t>
+  </si>
+  <si>
+    <t>0.0011,0.0020,0.9949,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.9921,0.0057,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9920,0.0000,0.9398</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0247,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9823,0.0159,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0015,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9765,0.9765,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5193,0.0039,0.5346,0.0001</t>
+  </si>
+  <si>
+    <t>0.9013,0.0169,0.0496,0.0019</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9954,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.7236,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.0742,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9918,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.1319,0.9982</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.6975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9302,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6184,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9870,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.5023,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0064,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9993,0.0003,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0047,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.4344,0.0017,0.5991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.2894,0.0001,0.8483,0.0000</t>
+    <t>0.9978,0.0007,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0070,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0016,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0007,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9984,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9976,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.8519,0.1800,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0682,0.0014,0.9179,0.0024</t>
+  </si>
+  <si>
+    <t>0.1049,0.0003,0.9314,0.0001</t>
+  </si>
+  <si>
+    <t>0.9446,0.0030,0.0328,0.0002</t>
+  </si>
+  <si>
+    <t>0.9245,0.0008,0.0744,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0177,0.0754,0.8577</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.2437,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.9914,0.0102,0.0001</t>
+  </si>
+  <si>
+    <t>0.9171,0.0334,0.0246,0.0002</t>
+  </si>
+  <si>
+    <t>0.7089,0.2641,0.0094,0.0006</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.7248,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.5176,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0143,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5936,0.0004,0.4951,0.0004</t>
+  </si>
+  <si>
+    <t>0.0419,0.0001,0.9780,0.0000</t>
+  </si>
+  <si>
+    <t>0.9359,0.0038,0.0275,0.0015</t>
+  </si>
+  <si>
+    <t>0.3032,0.0001,0.0002,0.8913</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0000,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.9584,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9934,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.9953,0.0003,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.5079,0.4802,0.0059,0.0009</t>
+  </si>
+  <si>
+    <t>0.9922,0.0002,0.0054,0.0004</t>
+  </si>
+  <si>
+    <t>0.0083,0.0000,0.0025,0.9930</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0078,0.0158,0.9923,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0001,0.0005,0.0051</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.8258,0.1978,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9714,0.0163,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.5623,0.2896,0.0188,0.0002</t>
+  </si>
+  <si>
+    <t>0.3589,0.1369,0.1497,0.0015</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0014,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0013,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.3494,0.6575,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.5641,0.2754,0.0348,0.0002</t>
+  </si>
+  <si>
+    <t>0.8148,0.1524,0.0064,0.0002</t>
+  </si>
+  <si>
+    <t>0.9890,0.0036,0.0046,0.0003</t>
+  </si>
+  <si>
+    <t>0.9934,0.0087,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0044,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9449,0.0890,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9800,0.0027,0.0112,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0015,0.9998,0.0003</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.9983,0.0000,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.3135,0.7364,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8540,0.0000,0.2038,0.0000</t>
-  </si>
-  <si>
-    <t>0.4012,0.0005,0.6474,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0005,0.9930,0.0007</t>
-  </si>
-  <si>
-    <t>0.0054,0.0002,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.1357,0.8314,0.0057,0.0005</t>
-  </si>
-  <si>
-    <t>0.9681,0.0067,0.0122,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0022</t>
-  </si>
-  <si>
-    <t>0.0041,0.9714,0.0179,0.0000</t>
-  </si>
-  <si>
-    <t>0.9932,0.0030,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.0030,0.0020,0.9969,0.0012</t>
-  </si>
-  <si>
-    <t>0.2705,0.8062,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.9938,0.0101,0.0006</t>
-  </si>
-  <si>
-    <t>0.0227,0.6469,0.2336,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0003,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0000,0.9973,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0182,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9990,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9181,0.0020,0.8422</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0704,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0001,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0102,0.0001,0.9943,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0020,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0005,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0019,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9942,0.0018,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9953,0.9761,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9986,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.4198,0.0045,0.6557,0.0001</t>
-  </si>
-  <si>
-    <t>0.8330,0.0019,0.2090,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.7992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9884,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.1602,0.9989</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0018,0.9995</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.0011,0.9987</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0005,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9380,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9181,0.9717,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9931,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.9482,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.1475,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0014,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9686,0.0508,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9894,0.0111,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9953,0.0032,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9918,0.0122,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0008,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9983,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.5895,0.4540,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.1078,0.0031,0.8640,0.0015</t>
-  </si>
-  <si>
-    <t>0.9957,0.0002,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.4995,0.0726,0.1561,0.0010</t>
-  </si>
-  <si>
-    <t>0.8742,0.0006,0.1304,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0045,0.0018,0.9950</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.8383,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9975,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.9460,0.0438,0.0073,0.0003</t>
-  </si>
-  <si>
-    <t>0.7207,0.2423,0.0113,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0002,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0009,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9236,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9822,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0019,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9111,0.0003,0.1236,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0001,0.9948,0.0001</t>
-  </si>
-  <si>
-    <t>0.9749,0.0003,0.0191,0.0002</t>
-  </si>
-  <si>
-    <t>0.4199,0.0001,0.0001,0.8195</t>
+    <t>0.0008,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0203,0.0063,0.9301,0.0025</t>
+  </si>
+  <si>
+    <t>0.0050,0.0008,0.9913,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0280,0.0250,0.8777,0.0005</t>
+  </si>
+  <si>
+    <t>0.0886,0.1507,0.4678,0.0003</t>
+  </si>
+  <si>
+    <t>0.9309,0.0009,0.0724,0.0000</t>
+  </si>
+  <si>
+    <t>0.4906,0.0036,0.4608,0.0027</t>
+  </si>
+  <si>
+    <t>0.0139,0.0028,0.9828,0.0005</t>
+  </si>
+  <si>
+    <t>0.0118,0.9890,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1107,0.8936,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.9959,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0049,0.9949,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8241,0.0346,0.0541,0.0006</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.4825,0.0058,0.0063,0.3861</t>
+  </si>
+  <si>
+    <t>0.2501,0.0010,0.7770,0.0003</t>
+  </si>
+  <si>
+    <t>0.7318,0.0016,0.2868,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.0052,0.9881,0.0012</t>
+  </si>
+  <si>
+    <t>0.0037,0.6631,0.6809,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0019,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0014,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0020,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0062,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0057,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0019,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0055,0.9982,0.0017</t>
+  </si>
+  <si>
+    <t>0.0244,0.0750,0.8935,0.0003</t>
+  </si>
+  <si>
+    <t>0.9085,0.0004,0.0717,0.0025</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0098,0.9895,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0011,0.9939,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0286,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0001,0.0044,0.0000</t>
+  </si>
+  <si>
+    <t>0.6896,0.0002,0.3448,0.0005</t>
+  </si>
+  <si>
+    <t>0.9644,0.0001,0.0438,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0025,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0060,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0445,0.0016,0.9408,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0117,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0035,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.0016,0.9877,0.0005</t>
+  </si>
+  <si>
+    <t>0.3508,0.0022,0.2486,0.0836</t>
+  </si>
+  <si>
+    <t>0.2752,0.0018,0.7270,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.0005,0.9945,0.0013</t>
+  </si>
+  <si>
+    <t>0.9728,0.0000,0.0011,0.0179</t>
+  </si>
+  <si>
+    <t>0.0011,0.0032,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0039,0.0000,0.0072,0.9964</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0001,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9882,0.9942,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0188,0.9704,0.0038,0.0034</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.0239,0.9687,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.2403,0.0000,0.0006,0.8836</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0335,0.0491,0.9602,0.0035</t>
-  </si>
-  <si>
-    <t>0.9934,0.0003,0.0024,0.0009</t>
-  </si>
-  <si>
-    <t>0.9966,0.0006,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9345,0.0256,0.0134,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9746,0.0209,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.0270,0.9715,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.2159,0.0064,0.7632,0.0008</t>
-  </si>
-  <si>
-    <t>0.9938,0.0006,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9966,0.0007,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9931,0.0024,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.2911,0.7218,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.4580,0.5242,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.9740,0.0201,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0117,0.3443,0.9531,0.0007</t>
-  </si>
-  <si>
-    <t>0.9984,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9889,0.0047,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.2017,0.8627,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9418,0.0123,0.0332,0.0016</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9993,0.0015</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9955,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0093,0.9878,0.0004</t>
-  </si>
-  <si>
-    <t>0.0055,0.0008,0.9932,0.0002</t>
-  </si>
-  <si>
-    <t>0.0117,0.0331,0.8903,0.0005</t>
-  </si>
-  <si>
-    <t>0.0015,0.1364,0.9756,0.0001</t>
-  </si>
-  <si>
-    <t>0.0274,0.0542,0.8698,0.0001</t>
-  </si>
-  <si>
-    <t>0.2313,0.0013,0.7958,0.0001</t>
-  </si>
-  <si>
-    <t>0.6467,0.0002,0.4098,0.0005</t>
-  </si>
-  <si>
-    <t>0.2424,0.0016,0.7872,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.9987,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0143,0.9855,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0699,0.9501,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.9934,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9255,0.0719,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.8675,0.0024,0.0931,0.0039</t>
-  </si>
-  <si>
-    <t>0.2782,0.0016,0.7235,0.0008</t>
-  </si>
-  <si>
-    <t>0.9498,0.0003,0.0452,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0077,0.0113,0.9800,0.0006</t>
-  </si>
-  <si>
-    <t>0.0017,0.8469,0.8837,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0003,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0007,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0011,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0048,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9974,0.0032,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0039,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0023,0.9993,0.0017</t>
-  </si>
-  <si>
-    <t>0.0779,0.2912,0.4804,0.0010</t>
-  </si>
-  <si>
-    <t>0.9827,0.0001,0.0073,0.0020</t>
-  </si>
-  <si>
-    <t>0.0000,0.0024,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0239,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.0009,0.9931,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0024,0.9980,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0726,0.9988,0.0005</t>
-  </si>
-  <si>
-    <t>0.9924,0.0000,0.0101,0.0000</t>
-  </si>
-  <si>
-    <t>0.3669,0.0001,0.7117,0.0002</t>
-  </si>
-  <si>
-    <t>0.9747,0.0002,0.0300,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0023,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9926,0.0062,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0013,0.9929,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0007,0.9944,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.0011,0.9947,0.0036</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0666,0.0008,0.9106,0.0021</t>
-  </si>
-  <si>
-    <t>0.9975,0.0000,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0061,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0271,0.0001,0.0041,0.9869</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9592,0.0026,0.0039,0.0133</t>
+    <t>0.9574,0.0020,0.0045,0.0106</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1872,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1907,7 +1886,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1921,7 +1900,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,7 +1914,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1949,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1963,7 +1942,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1977,7 +1956,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2005,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2019,7 +1998,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2033,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2047,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2058,10 +2037,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2075,7 +2054,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2086,10 +2065,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2103,7 +2082,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2117,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2131,7 +2110,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2145,7 +2124,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2156,10 +2135,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2173,7 +2152,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2187,7 +2166,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2201,7 +2180,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,10 +2191,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2229,7 +2208,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2243,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2257,7 +2236,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2271,7 +2250,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2285,7 +2264,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2299,7 +2278,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2313,7 +2292,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2327,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2341,7 +2320,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2355,7 +2334,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2366,10 +2345,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2383,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2397,7 +2376,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2411,7 +2390,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2425,7 +2404,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2439,7 +2418,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2453,7 +2432,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2467,7 +2446,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2481,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2495,7 +2474,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2509,7 +2488,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2523,7 +2502,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2537,7 +2516,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2551,7 +2530,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2565,7 +2544,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2579,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2593,7 +2572,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2607,7 +2586,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2621,7 +2600,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2635,7 +2614,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2649,7 +2628,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2663,7 +2642,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2677,7 +2656,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2691,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2705,7 +2684,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2719,7 +2698,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2733,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2747,7 +2726,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2761,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2775,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2789,7 +2768,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2803,7 +2782,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2817,7 +2796,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2831,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2842,10 +2821,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2859,7 +2838,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2873,7 +2852,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2887,7 +2866,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2901,7 +2880,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2912,10 +2891,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2929,7 +2908,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2943,7 +2922,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2957,7 +2936,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2971,7 +2950,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2985,7 +2964,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2999,7 +2978,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3013,7 +2992,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3094,7 +3073,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>348</v>
@@ -3125,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3139,7 +3118,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3153,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3167,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3181,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3195,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3209,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3223,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3237,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3251,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3265,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3279,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3293,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3307,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3321,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3335,7 +3314,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3349,7 +3328,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3363,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3377,7 +3356,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3391,7 +3370,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3405,7 +3384,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3419,7 +3398,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3433,7 +3412,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3447,7 +3426,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3461,7 +3440,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>281</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3475,7 +3454,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3489,7 +3468,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,10 +3479,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3517,7 +3496,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,7 +3510,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3545,7 +3524,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3559,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>286</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3573,7 +3552,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3587,7 +3566,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3598,10 +3577,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3615,7 +3594,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3629,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,7 +3622,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3657,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3671,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3685,7 +3664,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3699,7 +3678,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3713,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3727,7 +3706,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3741,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3755,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3769,7 +3748,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3783,7 +3762,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3797,7 +3776,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3811,7 +3790,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3825,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3839,7 +3818,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3853,7 +3832,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3867,7 +3846,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3881,7 +3860,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3895,7 +3874,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3909,7 +3888,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3923,7 +3902,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3937,7 +3916,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3951,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3965,7 +3944,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3979,7 +3958,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3990,10 +3969,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4007,7 +3986,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4021,7 +4000,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4035,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4049,7 +4028,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4063,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4077,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4091,7 +4070,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4105,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4119,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4130,10 +4109,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4144,10 +4123,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D163" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4161,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4175,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4189,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4203,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4217,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4231,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4245,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4259,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4273,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4287,7 +4266,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4298,10 +4277,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4315,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4326,10 +4305,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4343,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4357,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4371,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4382,10 +4361,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4399,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4413,7 +4392,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4427,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4441,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4455,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4469,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4483,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4497,7 +4476,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>327</v>
+        <v>431</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4511,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>434</v>
+        <v>308</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4525,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4539,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4553,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4567,7 +4546,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4578,10 +4557,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4592,10 +4571,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4606,10 +4585,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4623,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4637,7 +4616,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4651,7 +4630,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4665,7 +4644,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4679,7 +4658,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4693,7 +4672,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4707,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4721,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4732,10 +4711,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4749,7 +4728,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4763,7 +4742,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4777,7 +4756,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4791,7 +4770,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4805,7 +4784,7 @@
         <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4819,7 +4798,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4833,7 +4812,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4847,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4861,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4875,7 +4854,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4889,7 +4868,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4903,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4917,7 +4896,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4931,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>351</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4945,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4959,7 +4938,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4970,10 +4949,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4987,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5001,7 +4980,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5015,7 +4994,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5029,7 +5008,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5043,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5057,7 +5036,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5071,7 +5050,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>472</v>
+        <v>431</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5085,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5099,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5113,7 +5092,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5124,10 +5103,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5141,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5155,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5169,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5183,7 +5162,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5197,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5211,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>482</v>
+        <v>355</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5225,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5239,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5253,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>485</v>
+        <v>355</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5267,7 +5246,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5281,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5295,7 +5274,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5309,7 +5288,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5323,7 +5302,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5334,10 +5313,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D248" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5351,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5365,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5379,7 +5358,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5393,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5407,7 +5386,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5421,7 +5400,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>394</v>
+        <v>489</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5435,7 +5414,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>496</v>
+        <v>390</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5449,7 +5428,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
